--- a/archive/NEFTy_2026-09-05_2244_PT.xlsx
+++ b/archive/NEFTy_2026-09-05_2244_PT.xlsx
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.780701061260387</v>
+        <v>1.780701320170908</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1.311035712738891</v>
@@ -750,10 +750,10 @@
         <v>1.547923635217787</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.159521203031256</v>
+        <v>1.159521333839812</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>1.296873103076994</v>
+        <v>1.296873242205359</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.5248488768743713</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.536413562056367</v>
+        <v>1.536413373225165</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>1.139025500733548</v>
@@ -972,7 +972,7 @@
         <v>1.13271861918637</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5634508846038371</v>
+        <v>0.5634509855190464</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>-0.0397431750266648</v>
@@ -1134,10 +1134,10 @@
         <v>1.306341954937121</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.856822239098896</v>
+        <v>0.8568220940264304</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632233241123314</v>
+        <v>0.7632231863526957</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.1378121605773759</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740967483205673</v>
+        <v>0.8740969119018904</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.7605620540331652</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8320938409509537</v>
+        <v>0.832094036754814</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.6156588443481128</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.113680840244623</v>
+        <v>1.11368050503854</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.7272218190073159</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7050813018463387</v>
+        <v>0.7050811834036075</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.43361890634831</v>
@@ -1688,7 +1688,7 @@
         <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.367444342737236</v>
+        <v>0.3674444950892</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.03995183621570808</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.763198887475063</v>
+        <v>1.763199180820205</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.6674520561524815</v>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6695534891845289</v>
+        <v>0.6695536361980647</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3999390737344237</v>
+        <v>0.3999387636385074</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.381260960898314</v>
+        <v>0.3812606549397253</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.3528745980372852</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6565618098588615</v>
+        <v>0.6565620216387955</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.3219858657217809</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5545607742427558</v>
+        <v>0.5545609482485079</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.5137823270846265</v>
@@ -2010,13 +2010,13 @@
         <v>0.6640375198363835</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969983121244756</v>
+        <v>0.3969981893477683</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.377760354004183</v>
+        <v>0.3777602329182244</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3522537144371283</v>
+        <v>0.352253829479843</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.05321266058152796</v>
@@ -2066,10 +2066,10 @@
         <v>0.5455957151788788</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3671332428347083</v>
+        <v>0.3671331402761369</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3722462267693607</v>
+        <v>0.3722461238272272</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.1548263293356897</v>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6675999509793089</v>
+        <v>0.6675997834651819</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3869345103189425</v>
+        <v>0.386934394446645</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720418417781526</v>
+        <v>0.3720417271500722</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3458530565264364</v>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083086170660991</v>
+        <v>1.083085891569514</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.4595267581364666</v>
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5836572413313341</v>
+        <v>0.5836571353711313</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4824404283365684</v>
+        <v>0.4824403354880675</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3473148914530824</v>
+        <v>0.3473148070677907</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1454615380799074</v>
+        <v>0.1454616489492566</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0.119690129527162</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5662266246922192</v>
+        <v>0.5662267707694086</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.4830732318209987</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.544650718577969</v>
+        <v>0.5446505746326915</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.1788140589983993</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5426745803999016</v>
+        <v>0.5426742463901268</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.1826760187692307</v>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5589924853038439</v>
+        <v>0.5589922376025815</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870026424868</v>
+        <v>0.2867870870193954</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814583361875154</v>
+        <v>0.2814584202150137</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.2717691990035427</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5455964403920479</v>
+        <v>0.5455962817152487</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.333699585374126</v>
+        <v>0.3336997035251041</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.275338593485343</v>
+        <v>0.275338706466185</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.2708930358411168</v>
@@ -2826,10 +2826,10 @@
         <v>0.4418595202594637</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2641467152831039</v>
+        <v>0.264146797660618</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2737129077841483</v>
+        <v>0.2737129907850389</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.1847492268813271</v>
@@ -2878,10 +2878,10 @@
         <v>0.4337934514140818</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2722682033671824</v>
+        <v>0.2722681140079657</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2678493268287148</v>
+        <v>0.2678492377798629</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1885752537866485</v>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4508514368114691</v>
+        <v>0.4508513314638714</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2534754983218976</v>
+        <v>0.2534755769633175</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2670850367967565</v>
+        <v>0.2670851162920209</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0.2649924459663764</v>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3443246450418633</v>
+        <v>0.3443247906375415</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2690510772539778</v>
+        <v>0.2690509475067042</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2655668821105137</v>
+        <v>0.2655667527194627</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>0.129270688345682</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.3105532265789543</v>
+        <v>0.3105533207159228</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3029248468195411</v>
+        <v>0.3029247537752928</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2617404407419122</v>
+        <v>0.2617403506387177</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>0.1363270661486402</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270660758554026</v>
+        <v>0.4270662639822698</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.1263250787213801</v>
@@ -3520,7 +3520,7 @@
         <v>0.240744105364707</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08523357081287031</v>
+        <v>-0.08523349351222964</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>-0.0304502302686378</v>
@@ -3622,10 +3622,10 @@
         <v>0.2103107652399336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2796271277588027</v>
+        <v>0.2796270500822648</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2293427066468481</v>
+        <v>0.2293426320226992</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0.1482061450779253</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4408768111376706</v>
+        <v>0.4408766595046709</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2290598473281396</v>
+        <v>0.2290597370000531</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2217650253355736</v>
+        <v>0.221764915662316</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0.1879271316382964</v>
@@ -3726,10 +3726,10 @@
         <v>0.1755442130769598</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.269333942895492</v>
+        <v>0.2693337995003819</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.217509284976166</v>
+        <v>0.2175091474356246</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.1323776016142966</v>
@@ -3834,10 +3834,10 @@
         <v>0.319154269748813</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.194463451733716</v>
+        <v>0.1944635763351985</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2035901041379315</v>
+        <v>0.2035902296914684</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>0.1446617683774252</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3296584193612484</v>
+        <v>0.3296585139524517</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.2664747739759108</v>
@@ -3892,7 +3892,7 @@
         <v>0.2029491727456918</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1315250718642484</v>
+        <v>0.1315250033629372</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>0.1223255352865984</v>
@@ -3935,13 +3935,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3442858721527491</v>
+        <v>0.3442857163683846</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2007777249572409</v>
+        <v>0.2007776006587514</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1980471814095774</v>
+        <v>0.1980470573937401</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>0.151808910586533</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447652700247767</v>
+        <v>0.3447654126339179</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.2007974289088261</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3756670427192907</v>
+        <v>0.3756669252199267</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.2270838943447613</v>
@@ -4094,10 +4094,10 @@
         <v>0.3435590842611607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.199660912694537</v>
+        <v>0.1996610267455765</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1971219972480989</v>
+        <v>0.1971221110577652</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>0.1515557712139433</v>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.2597787759939749</v>
+        <v>0.2597786671955813</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1805259963985431</v>
+        <v>0.1805259008585947</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1932021448907368</v>
+        <v>0.1932020483249079</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0.1248023884404867</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.3200631311227193</v>
+        <v>0.3200630352564959</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1521995335328601</v>
+        <v>0.1521994604977654</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1656590319776483</v>
+        <v>0.1656589580893892</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.1774918875405691</v>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3329623165294675</v>
+        <v>0.3329624119123964</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0.157266693738918</v>
@@ -4626,10 +4626,10 @@
         <v>0.3382946371579334</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.14858002063956</v>
+        <v>0.1485799068394213</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.151566718262478</v>
+        <v>0.1515666041664203</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.1610479579021633</v>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1183228965709657</v>
+        <v>0.1183230276739218</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0.1120594594296969</v>
@@ -4688,7 +4688,7 @@
         <v>0.1420841480499133</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1047984789697887</v>
+        <v>0.1047983510186623</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.09269660865573459</v>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1355254539420063</v>
+        <v>0.1355253855311671</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.08641453385772246</v>
+        <v>0.08641465910040669</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1163324862504662</v>
+        <v>0.1163326149421147</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>-0.00338102769308779</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07915144326221046</v>
+        <v>0.07915153579447609</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0.09075567017467434</v>
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.2821676279453948</v>
+        <v>0.282167726665377</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.1029623485146134</v>
+        <v>0.1029624215674034</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.103917294270903</v>
+        <v>0.1039173673869422</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1072072188939013</v>
+        <v>0.107207292510076</v>
       </c>
       <c r="J82" s="3" t="n">
         <v>0.006896950376516386</v>
@@ -5051,16 +5051,16 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2794605910754389</v>
+        <v>0.2794606922784824</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1008469550706432</v>
+        <v>0.1008470299915947</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1016497767703139</v>
+        <v>0.1016498517459035</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1060873595664575</v>
+        <v>0.1060872839288154</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0.006754300246448297</v>
@@ -5158,13 +5158,13 @@
         <v>0.1834072518867882</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09141033178882241</v>
+        <v>0.09141025357922961</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08596267264564239</v>
+        <v>0.08596259482642443</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1588536212363327</v>
+        <v>0.1588535330622238</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0.1147901445543076</v>
@@ -5216,7 +5216,7 @@
         <v>0.08470351397488507</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.001559290331758945</v>
+        <v>-0.001559200409543493</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0.02069589958058415</v>
@@ -5483,16 +5483,16 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1850516411129475</v>
+        <v>0.1850515697269821</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511907901795675</v>
+        <v>0.04511919006318865</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156011538341487</v>
+        <v>0.05156022711301511</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1083125074517182</v>
+        <v>0.1083126323317054</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0.02400564571600916</v>
@@ -5539,16 +5539,16 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.2431670487492301</v>
+        <v>0.2431667795186294</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.01522076775004222</v>
+        <v>0.01522085752528057</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04141552668502424</v>
+        <v>0.04141561877664612</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.05954298579977202</v>
+        <v>0.05954308358488691</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0.06231378420201339</v>
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.08599336407834857</v>
+        <v>0.08599370508276771</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.03894933654575516</v>
+        <v>0.03894954461270528</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.0372025706220056</v>
+        <v>0.03720277833913666</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>0.02370734091802928</v>
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1207505468186056</v>
+        <v>0.1207504478549839</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.003725390809229623</v>
+        <v>-0.003725312607587683</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02209842567312537</v>
+        <v>0.02209850590178353</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>0.03465868209422918</v>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04850448717503664</v>
+        <v>0.04850428182646116</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0.02265642412273938</v>
@@ -5764,7 +5764,7 @@
         <v>0.02098221377412379</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.005218904814164871</v>
+        <v>0.005218810442326527</v>
       </c>
       <c r="J96" s="3" t="n">
         <v>0.006897335925965864</v>
@@ -5814,13 +5814,13 @@
         <v>0.04386089868234411</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.007972537081222919</v>
+        <v>0.007972392152186147</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.007030242477987114</v>
+        <v>0.007030097684436187</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.007196306180585532</v>
+        <v>-0.007196235880658097</v>
       </c>
       <c r="J97" s="5" t="n">
         <v>-0.004055951357985865</v>
@@ -5863,19 +5863,19 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808611220723557</v>
+        <v>0.03808619015196246</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.0001862028403939453</v>
+        <v>-0.0001861305370725042</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.003940580247929093</v>
+        <v>0.003940652849686144</v>
       </c>
       <c r="I98" s="5" t="n">
         <v>-0.01940796123955024</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01307885661499408</v>
+        <v>-0.01307892706561686</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>-0.004110584998271327</v>
@@ -5915,16 +5915,16 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410022876874885</v>
+        <v>0.03410049408896643</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.004237581373844668</v>
+        <v>-0.004237663377863576</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.0002734868428240222</v>
+        <v>-0.0002735691732980161</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.02395139583762362</v>
+        <v>-0.02395131704843334</v>
       </c>
       <c r="J99" s="5" t="n">
         <v>-0.00442454298082029</v>
@@ -5967,19 +5967,19 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.08907039377687376</v>
+        <v>0.089070562680853</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.004564860245733771</v>
+        <v>0.004564932100218577</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.004175442422483688</v>
+        <v>-0.004175371193174904</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0.00478065136126693</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.01032956152742326</v>
+        <v>0.01032948884590601</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.008776950318919008</v>
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03069234351705008</v>
+        <v>-0.0306921691281653</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.01436945990894378</v>
+        <v>-0.01436964022052767</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.01442943523621854</v>
+        <v>-0.01442961553683053</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04890658547240734</v>
+        <v>-0.04890666942067545</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>-0.02229630903445345</v>
